--- a/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
@@ -37,25 +37,25 @@
     <t>module_1</t>
   </si>
   <si>
-    <t>$O2'-4a-cyclic-tetrahydrobiopterin$$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$Indole-3-acetate$3,4-Dihydroxy-L-phenylalanine$4-(2-Aminophenyl)-2,4-dioxobutanoate$adrenochrome$L-Metanephrine$Tetrahydrobiopterin-4a-carbinolamine$methyl indole-3-acetate$3,4-Dihydroxyphenylacetaldehyde; Protocatechuatealdehyde$L-Tryptophan$3-Methoxytyramine$Formyl-N-acetyl-5-methoxykynurenamine$3-Methoxy-4-hydroxyphenylglycolaldehyde$D-Tryptophan$L-Normetanephrine$Serotonin$L-Kynurenine$S-aminomethyldihydrolipoamide$Formylkynurenine$N-Methylserotonin$$L-Formylkynurenine$Melatonin; N-Acetyl-5-methoxytryptamine$5-Hydroxykynurenamine$Indole-3-acetamide$6,7-Dihydrobiopterin$Indole-3-acetaldehyde$Tetrahydrobiopterin-4a-carbinolamine$6-Hydroxymelatonin$5-Hydroxyindoleacetaldehyde$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-hydroxytryptophol$5,10-Methylenetetrahydrofolate$3-O-methyldopa$enol-Phenylpyruvate$quinonoid dihydrobiopterin$Phenylpyruvate$N-Methylphenylethanolamine$5,10-Methenyltetrahydrofolate$5-Hydroxy-L-tryptophan$Citalopram$Formyl-5-hydroxykynurenamine$L-Tyrosine$2-Hydroxyphenylacetate</t>
-  </si>
-  <si>
-    <t>CE5860,CE5236,CE2173,C05639,C00954,C00355,C01252,CE5536,C05588,C15522,CE2122,C04043,C00078,C05587,C05642,C05583,C00525,C05589,C00780,C00328,alpam,C02406,C06212,CE3140,C02700,C01598,C05638,C02693,C00268,C00637,thbpt4acam,C05643,C05634,C00788,CE1918,C00143,CE2176,C02763,CE2705,C00166,C03711,C00445,C00643,C07572,C05647,C00082,C05852</t>
+    <t>$Serotonin$5-hydroxytryptophol$Citalopram$L-Normetanephrine$3,4-Dihydroxyphenylacetaldehyde; Protocatechuatealdehyde$5-Hydroxykynurenamine$N-Methylserotonin$Indole-3-acetaldehyde$3-Methoxy-4-hydroxyphenylglycolaldehyde$3-Methoxytyramine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$N-Methylphenylethanolamine$5-Hydroxyindoleacetaldehyde$adrenochrome$L-Metanephrine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol</t>
+  </si>
+  <si>
+    <t>CE2173,C00780,CE1918,C07572,C05589,C04043,C05638,C06212,C00637,C05583,C05587,C00788,C03711,C05634,CE5536,C05588,C05639</t>
+  </si>
+  <si>
+    <t>(8, 'Tyrosine metabolism');(7, 'Tryptophan metabolism');(2, 'Urea cycle/amino group metabolism')</t>
+  </si>
+  <si>
+    <t>module_2</t>
+  </si>
+  <si>
+    <t>L-Formylkynurenine$L-Tyrosine$Serotonin$L-Tryptophan$Indole-3-acetate$Formylkynurenine$6-Hydroxymelatonin$O2'-4a-cyclic-tetrahydrobiopterin$Formyl-5-hydroxykynurenamine$5-Hydroxyindoleacetaldehyde$$5-Hydroxy-L-tryptophan$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5,10-Methylenetetrahydrofolate$3-Methoxy-4-hydroxyphenylglycolaldehyde$Formyl-N-acetyl-5-methoxykynurenamine$Tetrahydrobiopterin-4a-carbinolamine$Indole-3-acetamide$L-Kynurenine$D-Tryptophan$3,4-Dihydroxy-L-phenylalanine$Citalopram$5-hydroxytryptophol$3,4-Dihydroxyphenylacetaldehyde; Protocatechuatealdehyde$5-Hydroxykynurenamine$quinonoid dihydrobiopterin$enol-Phenylpyruvate$Indole-3-acetaldehyde$Phenylpyruvate$5,10-Methenyltetrahydrofolate$$4-(2-Aminophenyl)-2,4-dioxobutanoate$L-Normetanephrine$N-Methylphenylethanolamine$adrenochrome$L-Metanephrine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$methyl indole-3-acetate$S-aminomethyldihydrolipoamide$6,7-Dihydrobiopterin$$Tetrahydrobiopterin-4a-carbinolamine$2-Hydroxyphenylacetate$3-O-methyldopa$N-Methylserotonin$Melatonin; N-Acetyl-5-methoxytryptamine$3-Methoxytyramine</t>
+  </si>
+  <si>
+    <t>C02700,C00082,C00780,C00078,C00954,C02406,C05643,CE5236,C05647,C05634,CE5860,C00643,C00788,C00143,C05583,C05642,thbpt4acam,C02693,C00328,C00525,C00355,C07572,CE1918,C04043,C05638,CE2705,C02763,C00637,C00166,C00445,CE3140,C01252,C05589,C03711,CE5536,C05588,C05639,CE2122,alpam,C00268,CE2173,C15522,C05852,CE2176,C06212,C01598,C05587</t>
   </si>
   <si>
     <t>(25, 'Tryptophan metabolism');(16, 'Tyrosine metabolism');(6, 'Biopterin metabolism')</t>
-  </si>
-  <si>
-    <t>module_2</t>
-  </si>
-  <si>
-    <t>adrenochrome$$5-Hydroxykynurenamine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$3,4-Dihydroxyphenylacetaldehyde; Protocatechuatealdehyde$3-Methoxytyramine$Indole-3-acetaldehyde$N-Methylphenylethanolamine$3-Methoxy-4-hydroxyphenylglycolaldehyde$5-hydroxytryptophol$Citalopram$5-Hydroxyindoleacetaldehyde$L-Normetanephrine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine</t>
-  </si>
-  <si>
-    <t>CE5536,CE2173,C05638,C05639,C04043,C05587,C00637,C03711,C05583,CE1918,C07572,C05634,C05589,C00788,C05588</t>
-  </si>
-  <si>
-    <t>(8, 'Tyrosine metabolism');(5, 'Tryptophan metabolism');(2, 'Urea cycle/amino group metabolism')</t>
   </si>
 </sst>
 </file>
@@ -415,10 +415,10 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.02183075759213228</v>
+        <v>0.01279132791327913</v>
       </c>
       <c r="C2">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -435,10 +435,10 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.03263806333081163</v>
+        <v>0.02146341463414634</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>

--- a/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
@@ -37,25 +37,25 @@
     <t>module_1</t>
   </si>
   <si>
-    <t>$Serotonin$5-hydroxytryptophol$Citalopram$L-Normetanephrine$3,4-Dihydroxyphenylacetaldehyde; Protocatechuatealdehyde$5-Hydroxykynurenamine$N-Methylserotonin$Indole-3-acetaldehyde$3-Methoxy-4-hydroxyphenylglycolaldehyde$3-Methoxytyramine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$N-Methylphenylethanolamine$5-Hydroxyindoleacetaldehyde$adrenochrome$L-Metanephrine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol</t>
-  </si>
-  <si>
-    <t>CE2173,C00780,CE1918,C07572,C05589,C04043,C05638,C06212,C00637,C05583,C05587,C00788,C03711,C05634,CE5536,C05588,C05639</t>
-  </si>
-  <si>
-    <t>(8, 'Tyrosine metabolism');(7, 'Tryptophan metabolism');(2, 'Urea cycle/amino group metabolism')</t>
+    <t>L-Normetanephrine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$3-Methoxy-4-hydroxyphenylglycolaldehyde$5-Hydroxyindoleacetaldehyde$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$5-Hydroxykynurenamine$S-Adenosyl-L-homocysteine$L-Metanephrine$3-Methoxytyramine$Indole-3-acetaldehyde$Serotonin$$adrenochrome$Hypoxanthine$Xanthosine$Thymidine$Deoxyguanosine$Deoxyuridine$Adenosine$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$5-Hydroxy-L-tryptophan$Formyl-5-hydroxykynurenamine$Formyl-N-acetyl-5-methoxykynurenamine$L-Formylkynurenine$Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$o-methylhippurate$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Methoxyindoleacetate$5-Hydroxyindoleacetate$methyl indole-3-acetate$Indole-3-acetate$L-Kynurenine$Formylkynurenine$4-(2-Aminophenyl)-2,4-dioxobutanoate$Homovanillate; Homovanillic acid$enol-Phenylpyruvate$Phenylpyruvate$L-Tyrosine$L-Phenylalanine$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$5-Phenyl-1,3-oxazinane-2,4-dione$2-Phenyl-1,3-propanediol monocarbamate$3,4-Dihydroxyphenylethyleneglycol$3-Carbamoyl-2-phenylpropionaldehyde$3-Carbamoyl-2-phenylpropionic acid$Tetrahydrobiopterin-4a-carbinolamine$6,7-Dihydrobiopterin$Tetrahydrobiopterin-4a-carbinolamine$3-O-methyldopa$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$Epinine; Deoxyepinephrine$5-methoxytryptophol$5-hydroxytryptophol$Uridine$Cytidine$quinonoid dihydrobiopterin$O2'-4a-cyclic-tetrahydrobiopterin$Nicotinate D-ribonucleotide$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC$11beta,17alpha,21-Trihydroxypregnenolone$17alpha,21-Dihydroxypregnenolone$Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$11-Deoxycortisol; Cortodoxone$Androstenedione$17alpha-Hydroxyprogesterone$11beta-Hydroxyprogesterone$11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione$Estradiol-17beta; beta-Estradiol; Estradiol$21-Hydroxy-5beta-pregnane-3,11,20-trione$21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone$Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$2-Hydroxyestradiol-17beta; 2-OH-Estradiol$4,17 dihydroxy estradiol$4-hydroxy-17beta-estradiol$Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol$3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione</t>
+  </si>
+  <si>
+    <t>C05589,C00788,C05583,C05634,C05639,C05638,C00021,C05588,C05587,C00637,C00780,CE2173,CE5536,C00262,C01762,C00214,C00330,C00526,C00212,C00978,C00643,C05647,C05642,C02700,C01586,CE2934,C09642,C05660,C05635,CE2122,C00954,C00328,C02406,C01252,C05582,C02763,C00166,C00082,C00079,C16595,C16596,C16586,C05576,C16587,C16591,thbpt4acam,C00268,C15522,CE2176,C00355,C05580,C07453,CE6205,CE1918,C00299,C00475,CE2705,CE5236,C01185,C04692,CE5860,C05139,C01176,C03205,C05489,C05487,C00280,C05488,andrstndn,17ahprgstrn,C05498,C05475,C00951,C05477,C05497,C02140,C05301,hestratriol,CE2179,C05141,C05478</t>
+  </si>
+  <si>
+    <t>(23, 'Tryptophan metabolism');(21, 'Tyrosine metabolism');(18, 'C21-steroid hormone biosynthesis and metabolism')</t>
   </si>
   <si>
     <t>module_2</t>
   </si>
   <si>
-    <t>L-Formylkynurenine$L-Tyrosine$Serotonin$L-Tryptophan$Indole-3-acetate$Formylkynurenine$6-Hydroxymelatonin$O2'-4a-cyclic-tetrahydrobiopterin$Formyl-5-hydroxykynurenamine$5-Hydroxyindoleacetaldehyde$$5-Hydroxy-L-tryptophan$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5,10-Methylenetetrahydrofolate$3-Methoxy-4-hydroxyphenylglycolaldehyde$Formyl-N-acetyl-5-methoxykynurenamine$Tetrahydrobiopterin-4a-carbinolamine$Indole-3-acetamide$L-Kynurenine$D-Tryptophan$3,4-Dihydroxy-L-phenylalanine$Citalopram$5-hydroxytryptophol$3,4-Dihydroxyphenylacetaldehyde; Protocatechuatealdehyde$5-Hydroxykynurenamine$quinonoid dihydrobiopterin$enol-Phenylpyruvate$Indole-3-acetaldehyde$Phenylpyruvate$5,10-Methenyltetrahydrofolate$$4-(2-Aminophenyl)-2,4-dioxobutanoate$L-Normetanephrine$N-Methylphenylethanolamine$adrenochrome$L-Metanephrine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$methyl indole-3-acetate$S-aminomethyldihydrolipoamide$6,7-Dihydrobiopterin$$Tetrahydrobiopterin-4a-carbinolamine$2-Hydroxyphenylacetate$3-O-methyldopa$N-Methylserotonin$Melatonin; N-Acetyl-5-methoxytryptamine$3-Methoxytyramine</t>
-  </si>
-  <si>
-    <t>C02700,C00082,C00780,C00078,C00954,C02406,C05643,CE5236,C05647,C05634,CE5860,C00643,C00788,C00143,C05583,C05642,thbpt4acam,C02693,C00328,C00525,C00355,C07572,CE1918,C04043,C05638,CE2705,C02763,C00637,C00166,C00445,CE3140,C01252,C05589,C03711,CE5536,C05588,C05639,CE2122,alpam,C00268,CE2173,C15522,C05852,CE2176,C06212,C01598,C05587</t>
-  </si>
-  <si>
-    <t>(25, 'Tryptophan metabolism');(16, 'Tyrosine metabolism');(6, 'Biopterin metabolism')</t>
+    <t>4,6-Dihydroxyquinoline; Quinoline-4,6-diol$$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Hydroxyindoleacetaldehyde$Serotonin$L-Normetanephrine$L-Metanephrine$adrenochrome$Indole-3-acetaldehyde$5-Hydroxykynurenamine$3-Methoxytyramine$3-Methoxy-4-hydroxyphenylglycolaldehyde</t>
+  </si>
+  <si>
+    <t>C05639,CE2173,C00788,C05634,C00780,C05589,C05588,CE5536,C00637,C05638,C05587,C05583</t>
+  </si>
+  <si>
+    <t>(7, 'Tyrosine metabolism');(5, 'Tryptophan metabolism');(1, 'Urea cycle/amino group metabolism')</t>
   </si>
 </sst>
 </file>
@@ -415,10 +415,10 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.01279132791327913</v>
+        <v>0.04721076622530931</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -435,10 +435,10 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.02146341463414634</v>
+        <v>0.04753635771651834</v>
       </c>
       <c r="C3">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>

--- a/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>MODULE</t>
   </si>
@@ -32,30 +32,6 @@
   </si>
   <si>
     <t>This module overlaps with</t>
-  </si>
-  <si>
-    <t>module_1</t>
-  </si>
-  <si>
-    <t>L-Normetanephrine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$3-Methoxy-4-hydroxyphenylglycolaldehyde$5-Hydroxyindoleacetaldehyde$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$5-Hydroxykynurenamine$S-Adenosyl-L-homocysteine$L-Metanephrine$3-Methoxytyramine$Indole-3-acetaldehyde$Serotonin$$adrenochrome$Hypoxanthine$Xanthosine$Thymidine$Deoxyguanosine$Deoxyuridine$Adenosine$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$5-Hydroxy-L-tryptophan$Formyl-5-hydroxykynurenamine$Formyl-N-acetyl-5-methoxykynurenamine$L-Formylkynurenine$Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$o-methylhippurate$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Methoxyindoleacetate$5-Hydroxyindoleacetate$methyl indole-3-acetate$Indole-3-acetate$L-Kynurenine$Formylkynurenine$4-(2-Aminophenyl)-2,4-dioxobutanoate$Homovanillate; Homovanillic acid$enol-Phenylpyruvate$Phenylpyruvate$L-Tyrosine$L-Phenylalanine$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$5-Phenyl-1,3-oxazinane-2,4-dione$2-Phenyl-1,3-propanediol monocarbamate$3,4-Dihydroxyphenylethyleneglycol$3-Carbamoyl-2-phenylpropionaldehyde$3-Carbamoyl-2-phenylpropionic acid$Tetrahydrobiopterin-4a-carbinolamine$6,7-Dihydrobiopterin$Tetrahydrobiopterin-4a-carbinolamine$3-O-methyldopa$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$Epinine; Deoxyepinephrine$5-methoxytryptophol$5-hydroxytryptophol$Uridine$Cytidine$quinonoid dihydrobiopterin$O2'-4a-cyclic-tetrahydrobiopterin$Nicotinate D-ribonucleotide$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC$11beta,17alpha,21-Trihydroxypregnenolone$17alpha,21-Dihydroxypregnenolone$Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$11-Deoxycortisol; Cortodoxone$Androstenedione$17alpha-Hydroxyprogesterone$11beta-Hydroxyprogesterone$11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione$Estradiol-17beta; beta-Estradiol; Estradiol$21-Hydroxy-5beta-pregnane-3,11,20-trione$21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone$Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$2-Hydroxyestradiol-17beta; 2-OH-Estradiol$4,17 dihydroxy estradiol$4-hydroxy-17beta-estradiol$Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol$3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione</t>
-  </si>
-  <si>
-    <t>C05589,C00788,C05583,C05634,C05639,C05638,C00021,C05588,C05587,C00637,C00780,CE2173,CE5536,C00262,C01762,C00214,C00330,C00526,C00212,C00978,C00643,C05647,C05642,C02700,C01586,CE2934,C09642,C05660,C05635,CE2122,C00954,C00328,C02406,C01252,C05582,C02763,C00166,C00082,C00079,C16595,C16596,C16586,C05576,C16587,C16591,thbpt4acam,C00268,C15522,CE2176,C00355,C05580,C07453,CE6205,CE1918,C00299,C00475,CE2705,CE5236,C01185,C04692,CE5860,C05139,C01176,C03205,C05489,C05487,C00280,C05488,andrstndn,17ahprgstrn,C05498,C05475,C00951,C05477,C05497,C02140,C05301,hestratriol,CE2179,C05141,C05478</t>
-  </si>
-  <si>
-    <t>(23, 'Tryptophan metabolism');(21, 'Tyrosine metabolism');(18, 'C21-steroid hormone biosynthesis and metabolism')</t>
-  </si>
-  <si>
-    <t>module_2</t>
-  </si>
-  <si>
-    <t>4,6-Dihydroxyquinoline; Quinoline-4,6-diol$$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Hydroxyindoleacetaldehyde$Serotonin$L-Normetanephrine$L-Metanephrine$adrenochrome$Indole-3-acetaldehyde$5-Hydroxykynurenamine$3-Methoxytyramine$3-Methoxy-4-hydroxyphenylglycolaldehyde</t>
-  </si>
-  <si>
-    <t>C05639,CE2173,C00788,C05634,C00780,C05589,C05588,CE5536,C00637,C05638,C05587,C05583</t>
-  </si>
-  <si>
-    <t>(7, 'Tyrosine metabolism');(5, 'Tryptophan metabolism');(1, 'Urea cycle/amino group metabolism')</t>
   </si>
 </sst>
 </file>
@@ -387,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -410,46 +386,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>0.04721076622530931</v>
-      </c>
-      <c r="C2">
-        <v>81</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3">
-        <v>0.04753635771651834</v>
-      </c>
-      <c r="C3">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>MODULE</t>
   </si>
@@ -32,6 +32,30 @@
   </si>
   <si>
     <t>This module overlaps with</t>
+  </si>
+  <si>
+    <t>module_1</t>
+  </si>
+  <si>
+    <t>L-Normetanephrine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$3-Methoxy-4-hydroxyphenylglycolaldehyde$5-Hydroxyindoleacetaldehyde$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$5-Hydroxykynurenamine$S-Adenosyl-L-homocysteine$L-Metanephrine$3-Methoxytyramine$Indole-3-acetaldehyde$Serotonin$$adrenochrome$Hypoxanthine$Xanthosine$Thymidine$Deoxyguanosine$Deoxyuridine$Adenosine$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$5-Hydroxy-L-tryptophan$Formyl-5-hydroxykynurenamine$Formyl-N-acetyl-5-methoxykynurenamine$L-Formylkynurenine$Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$o-methylhippurate$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Methoxyindoleacetate$5-Hydroxyindoleacetate$methyl indole-3-acetate$Indole-3-acetate$L-Kynurenine$Formylkynurenine$4-(2-Aminophenyl)-2,4-dioxobutanoate$Homovanillate; Homovanillic acid$enol-Phenylpyruvate$Phenylpyruvate$L-Tyrosine$L-Phenylalanine$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$5-Phenyl-1,3-oxazinane-2,4-dione$2-Phenyl-1,3-propanediol monocarbamate$3,4-Dihydroxyphenylethyleneglycol$3-Carbamoyl-2-phenylpropionaldehyde$3-Carbamoyl-2-phenylpropionic acid$Tetrahydrobiopterin-4a-carbinolamine$6,7-Dihydrobiopterin$Tetrahydrobiopterin-4a-carbinolamine$3-O-methyldopa$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$Epinine; Deoxyepinephrine$5-methoxytryptophol$5-hydroxytryptophol$Uridine$Cytidine$quinonoid dihydrobiopterin$O2'-4a-cyclic-tetrahydrobiopterin$Nicotinate D-ribonucleotide$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC$11beta,17alpha,21-Trihydroxypregnenolone$17alpha,21-Dihydroxypregnenolone$Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$11-Deoxycortisol; Cortodoxone$Androstenedione$17alpha-Hydroxyprogesterone$11beta-Hydroxyprogesterone$11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione$Estradiol-17beta; beta-Estradiol; Estradiol$21-Hydroxy-5beta-pregnane-3,11,20-trione$21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone$Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$2-Hydroxyestradiol-17beta; 2-OH-Estradiol$4,17 dihydroxy estradiol$4-hydroxy-17beta-estradiol$Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol$3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione</t>
+  </si>
+  <si>
+    <t>C05589,C00788,C05583,C05634,C05639,C05638,C00021,C05588,C05587,C00637,C00780,CE2173,CE5536,C00262,C01762,C00214,C00330,C00526,C00212,C00978,C00643,C05647,C05642,C02700,C01586,CE2934,C09642,C05660,C05635,CE2122,C00954,C00328,C02406,C01252,C05582,C02763,C00166,C00082,C00079,C16595,C16596,C16586,C05576,C16587,C16591,thbpt4acam,C00268,C15522,CE2176,C00355,C05580,C07453,CE6205,CE1918,C00299,C00475,CE2705,CE5236,C01185,C04692,CE5860,C05139,C01176,C03205,C05489,C05487,C00280,C05488,andrstndn,17ahprgstrn,C05498,C05475,C00951,C05477,C05497,C02140,C05301,hestratriol,CE2179,C05141,C05478</t>
+  </si>
+  <si>
+    <t>(23, 'Tryptophan metabolism');(21, 'Tyrosine metabolism');(18, 'C21-steroid hormone biosynthesis and metabolism')</t>
+  </si>
+  <si>
+    <t>module_2</t>
+  </si>
+  <si>
+    <t>Serotonin$5-Hydroxyindoleacetaldehyde$$adrenochrome$3-Methoxytyramine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine$5-Hydroxykynurenamine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$Indole-3-acetaldehyde$3-Methoxy-4-hydroxyphenylglycolaldehyde$L-Normetanephrine</t>
+  </si>
+  <si>
+    <t>C00780,C05634,CE2173,CE5536,C05587,C00788,C05588,C05638,C05639,C00637,C05583,C05589</t>
+  </si>
+  <si>
+    <t>(7, 'Tyrosine metabolism');(5, 'Tryptophan metabolism');(1, 'Urea cycle/amino group metabolism')</t>
   </si>
 </sst>
 </file>
@@ -363,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -386,6 +410,46 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>0.04878572963679347</v>
+      </c>
+      <c r="C2">
+        <v>81</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>0.04932301740812379</v>
+      </c>
+      <c r="C3">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>MODULE</t>
   </si>
@@ -44,18 +44,6 @@
   </si>
   <si>
     <t>(23, 'Tryptophan metabolism');(21, 'Tyrosine metabolism');(18, 'C21-steroid hormone biosynthesis and metabolism')</t>
-  </si>
-  <si>
-    <t>module_2</t>
-  </si>
-  <si>
-    <t>Serotonin$5-Hydroxyindoleacetaldehyde$$adrenochrome$3-Methoxytyramine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$L-Metanephrine$5-Hydroxykynurenamine$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$Indole-3-acetaldehyde$3-Methoxy-4-hydroxyphenylglycolaldehyde$L-Normetanephrine</t>
-  </si>
-  <si>
-    <t>C00780,C05634,CE2173,CE5536,C05587,C00788,C05588,C05638,C05639,C00637,C05583,C05589</t>
-  </si>
-  <si>
-    <t>(7, 'Tyrosine metabolism');(5, 'Tryptophan metabolism');(1, 'Urea cycle/amino group metabolism')</t>
   </si>
 </sst>
 </file>
@@ -387,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -415,7 +403,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.04878572963679347</v>
+        <v>0.04982780886784331</v>
       </c>
       <c r="C2">
         <v>81</v>
@@ -428,26 +416,6 @@
       </c>
       <c r="F2" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3">
-        <v>0.04932301740812379</v>
-      </c>
-      <c r="C3">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>MODULE</t>
   </si>
@@ -37,13 +37,25 @@
     <t>module_1</t>
   </si>
   <si>
-    <t>L-Normetanephrine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$3-Methoxy-4-hydroxyphenylglycolaldehyde$5-Hydroxyindoleacetaldehyde$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$5-Hydroxykynurenamine$S-Adenosyl-L-homocysteine$L-Metanephrine$3-Methoxytyramine$Indole-3-acetaldehyde$Serotonin$$adrenochrome$Hypoxanthine$Xanthosine$Thymidine$Deoxyguanosine$Deoxyuridine$Adenosine$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$5-Hydroxy-L-tryptophan$Formyl-5-hydroxykynurenamine$Formyl-N-acetyl-5-methoxykynurenamine$L-Formylkynurenine$Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$o-methylhippurate$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Methoxyindoleacetate$5-Hydroxyindoleacetate$methyl indole-3-acetate$Indole-3-acetate$L-Kynurenine$Formylkynurenine$4-(2-Aminophenyl)-2,4-dioxobutanoate$Homovanillate; Homovanillic acid$enol-Phenylpyruvate$Phenylpyruvate$L-Tyrosine$L-Phenylalanine$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$5-Phenyl-1,3-oxazinane-2,4-dione$2-Phenyl-1,3-propanediol monocarbamate$3,4-Dihydroxyphenylethyleneglycol$3-Carbamoyl-2-phenylpropionaldehyde$3-Carbamoyl-2-phenylpropionic acid$Tetrahydrobiopterin-4a-carbinolamine$6,7-Dihydrobiopterin$Tetrahydrobiopterin-4a-carbinolamine$3-O-methyldopa$3,4-Dihydroxy-L-phenylalanine$3,4-Dihydroxymandelate$Epinine; Deoxyepinephrine$5-methoxytryptophol$5-hydroxytryptophol$Uridine$Cytidine$quinonoid dihydrobiopterin$O2'-4a-cyclic-tetrahydrobiopterin$Nicotinate D-ribonucleotide$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC$11beta,17alpha,21-Trihydroxypregnenolone$17alpha,21-Dihydroxypregnenolone$Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$11-Deoxycortisol; Cortodoxone$Androstenedione$17alpha-Hydroxyprogesterone$11beta-Hydroxyprogesterone$11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione$Estradiol-17beta; beta-Estradiol; Estradiol$21-Hydroxy-5beta-pregnane-3,11,20-trione$21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone$Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$2-Hydroxyestradiol-17beta; 2-OH-Estradiol$4,17 dihydroxy estradiol$4-hydroxy-17beta-estradiol$Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol$3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione</t>
-  </si>
-  <si>
-    <t>C05589,C00788,C05583,C05634,C05639,C05638,C00021,C05588,C05587,C00637,C00780,CE2173,CE5536,C00262,C01762,C00214,C00330,C00526,C00212,C00978,C00643,C05647,C05642,C02700,C01586,CE2934,C09642,C05660,C05635,CE2122,C00954,C00328,C02406,C01252,C05582,C02763,C00166,C00082,C00079,C16595,C16596,C16586,C05576,C16587,C16591,thbpt4acam,C00268,C15522,CE2176,C00355,C05580,C07453,CE6205,CE1918,C00299,C00475,CE2705,CE5236,C01185,C04692,CE5860,C05139,C01176,C03205,C05489,C05487,C00280,C05488,andrstndn,17ahprgstrn,C05498,C05475,C00951,C05477,C05497,C02140,C05301,hestratriol,CE2179,C05141,C05478</t>
-  </si>
-  <si>
-    <t>(23, 'Tryptophan metabolism');(21, 'Tyrosine metabolism');(18, 'C21-steroid hormone biosynthesis and metabolism')</t>
+    <t>Serotonin$5-Hydroxyindoleacetaldehyde$adrenochrome$Indole-3-acetaldehyde$L-Normetanephrine$5-Hydroxykynurenamine$$L-Metanephrine$Citalopram$3-Methoxytyramine$3-Methoxy-4-hydroxyphenylglycolaldehyde$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
+  </si>
+  <si>
+    <t>C00780,C05634,CE5536,C00637,C05589,C05638,CE2173,C05588,C07572,C05587,C05583,C05639,C00788</t>
+  </si>
+  <si>
+    <t>(7, 'Tyrosine metabolism');(5, 'Tryptophan metabolism');(1, 'Urea cycle/amino group metabolism')</t>
+  </si>
+  <si>
+    <t>module_2</t>
+  </si>
+  <si>
+    <t>L-Normetanephrine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$3-Methoxy-4-hydroxyphenylglycolaldehyde$5-Hydroxyindoleacetaldehyde$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$5-Hydroxykynurenamine$Citalopram$S-Adenosyl-L-homocysteine$L-Metanephrine$3-Methoxytyramine$Indole-3-acetaldehyde$Serotonin$$adrenochrome$Hypoxanthine$Thymidine$Deoxyguanosine$Deoxyuridine$Adenosine$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$5-Hydroxy-L-tryptophan$Formyl-5-hydroxykynurenamine$Formyl-N-acetyl-5-methoxykynurenamine$Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$o-methylhippurate$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Methoxyindoleacetate$5-Hydroxyindoleacetate$methyl indole-3-acetate$Indole-3-acetate$Homovanillate; Homovanillic acid$enol-Phenylpyruvate$Phenylpyruvate$L-Tyrosine$3,4-Dihydroxy-L-phenylalanine$6,7-Dihydrobiopterin$Tetrahydrobiopterin-4a-carbinolamine$Tetrahydrobiopterin-4a-carbinolamine$Epinine; Deoxyepinephrine$3-O-methyldopa$5-Phenyl-1,3-oxazinane-2,4-dione$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$3-Carbamoyl-2-phenylpropionaldehyde$2-Phenyl-1,3-propanediol monocarbamate$3,4-Dihydroxyphenylethyleneglycol$3-Carbamoyl-2-phenylpropionic acid$5-methoxytryptophol$5-hydroxytryptophol$Uridine$Cytidine$quinonoid dihydrobiopterin$O2'-4a-cyclic-tetrahydrobiopterin$Nicotinate D-ribonucleotide$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$$$3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA$6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one$Testosterone$19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$5beta-Androstane-3,17-dione$11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC$11beta,17alpha,21-Trihydroxypregnenolone$17alpha,21-Dihydroxypregnenolone$Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$11-Deoxycortisol; Cortodoxone$Androstenedione$17alpha-Hydroxyprogesterone$Estrone; 3-Hydroxy-1,3,5(10)-estratrien-17-one$11beta-Hydroxyprogesterone$11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione$5alpha-Androstane-3,17-dione; Androstanedione$Estradiol-17beta; beta-Estradiol; Estradiol$21-Hydroxy-5beta-pregnane-3,11,20-trione$21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone$Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$2-Hydroxyestradiol-17beta; 2-OH-Estradiol$4,17 dihydroxy estradiol$4-hydroxy-17beta-estradiol$Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol$3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Estrone 3-sulfate</t>
+  </si>
+  <si>
+    <t>C05589,C00788,C05583,C05634,C05639,C05638,C07572,C00021,C05588,C05587,C00637,C00780,CE2173,CE5536,C00262,C00214,C00330,C00526,C00212,C00978,C00643,C05647,C05642,C01586,CE2934,C09642,C05660,C05635,CE2122,C00954,C05582,C02763,C00166,C00082,C00355,C00268,C15522,thbpt4acam,C07453,CE2176,C16596,C16595,C16587,C16586,C05576,C16591,CE6205,CE1918,C00299,C00475,CE2705,CE5236,C01185,C04692,CE5860,C18045,C01227,C14497,C00535,C05294,C05139,C01176,C03772,C03205,C05489,C05487,C00280,C05488,andrstndn,17ahprgstrn,C00468,C05498,C05475,C00674,C00951,C05477,C05497,C02140,C05301,hestratriol,CE2179,C05141,C05478,C02538</t>
+  </si>
+  <si>
+    <t>(23, 'C21-steroid hormone biosynthesis and metabolism');(19, 'Tyrosine metabolism');(19, 'Tryptophan metabolism')</t>
   </si>
 </sst>
 </file>
@@ -375,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -403,10 +415,10 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.04982780886784331</v>
+        <v>0.03854649878506737</v>
       </c>
       <c r="C2">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -416,6 +428,26 @@
       </c>
       <c r="F2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>0.04694057874972388</v>
+      </c>
+      <c r="C3">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
+++ b/results/pathways/PC_vs_Control/mcg_modularanalysis_PC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>MODULE</t>
   </si>
@@ -32,30 +32,6 @@
   </si>
   <si>
     <t>This module overlaps with</t>
-  </si>
-  <si>
-    <t>module_1</t>
-  </si>
-  <si>
-    <t>Serotonin$5-Hydroxyindoleacetaldehyde$adrenochrome$Indole-3-acetaldehyde$L-Normetanephrine$5-Hydroxykynurenamine$$L-Metanephrine$Citalopram$3-Methoxytyramine$3-Methoxy-4-hydroxyphenylglycolaldehyde$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
-  </si>
-  <si>
-    <t>C00780,C05634,CE5536,C00637,C05589,C05638,CE2173,C05588,C07572,C05587,C05583,C05639,C00788</t>
-  </si>
-  <si>
-    <t>(7, 'Tyrosine metabolism');(5, 'Tryptophan metabolism');(1, 'Urea cycle/amino group metabolism')</t>
-  </si>
-  <si>
-    <t>module_2</t>
-  </si>
-  <si>
-    <t>L-Normetanephrine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$3-Methoxy-4-hydroxyphenylglycolaldehyde$5-Hydroxyindoleacetaldehyde$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$5-Hydroxykynurenamine$Citalopram$S-Adenosyl-L-homocysteine$L-Metanephrine$3-Methoxytyramine$Indole-3-acetaldehyde$Serotonin$$adrenochrome$Hypoxanthine$Thymidine$Deoxyguanosine$Deoxyuridine$Adenosine$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$5-Hydroxy-L-tryptophan$Formyl-5-hydroxykynurenamine$Formyl-N-acetyl-5-methoxykynurenamine$Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$o-methylhippurate$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Methoxyindoleacetate$5-Hydroxyindoleacetate$methyl indole-3-acetate$Indole-3-acetate$Homovanillate; Homovanillic acid$enol-Phenylpyruvate$Phenylpyruvate$L-Tyrosine$3,4-Dihydroxy-L-phenylalanine$6,7-Dihydrobiopterin$Tetrahydrobiopterin-4a-carbinolamine$Tetrahydrobiopterin-4a-carbinolamine$Epinine; Deoxyepinephrine$3-O-methyldopa$5-Phenyl-1,3-oxazinane-2,4-dione$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$3-Carbamoyl-2-phenylpropionaldehyde$2-Phenyl-1,3-propanediol monocarbamate$3,4-Dihydroxyphenylethyleneglycol$3-Carbamoyl-2-phenylpropionic acid$5-methoxytryptophol$5-hydroxytryptophol$Uridine$Cytidine$quinonoid dihydrobiopterin$O2'-4a-cyclic-tetrahydrobiopterin$Nicotinate D-ribonucleotide$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$$$3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA$6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one$Testosterone$19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one$16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$5beta-Androstane-3,17-dione$11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC$11beta,17alpha,21-Trihydroxypregnenolone$17alpha,21-Dihydroxypregnenolone$Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$11-Deoxycortisol; Cortodoxone$Androstenedione$17alpha-Hydroxyprogesterone$Estrone; 3-Hydroxy-1,3,5(10)-estratrien-17-one$11beta-Hydroxyprogesterone$11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione$5alpha-Androstane-3,17-dione; Androstanedione$Estradiol-17beta; beta-Estradiol; Estradiol$21-Hydroxy-5beta-pregnane-3,11,20-trione$21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone$Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$2-Hydroxyestradiol-17beta; 2-OH-Estradiol$4,17 dihydroxy estradiol$4-hydroxy-17beta-estradiol$Estriol; 1,3,5(10)-Estratriene-3,16-alpha,17beta-triol$3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Estrone 3-sulfate</t>
-  </si>
-  <si>
-    <t>C05589,C00788,C05583,C05634,C05639,C05638,C07572,C00021,C05588,C05587,C00637,C00780,CE2173,CE5536,C00262,C00214,C00330,C00526,C00212,C00978,C00643,C05647,C05642,C01586,CE2934,C09642,C05660,C05635,CE2122,C00954,C05582,C02763,C00166,C00082,C00355,C00268,C15522,thbpt4acam,C07453,CE2176,C16596,C16595,C16587,C16586,C05576,C16591,CE6205,CE1918,C00299,C00475,CE2705,CE5236,C01185,C04692,CE5860,C18045,C01227,C14497,C00535,C05294,C05139,C01176,C03772,C03205,C05489,C05487,C00280,C05488,andrstndn,17ahprgstrn,C00468,C05498,C05475,C00674,C00951,C05477,C05497,C02140,C05301,hestratriol,CE2179,C05141,C05478,C02538</t>
-  </si>
-  <si>
-    <t>(23, 'C21-steroid hormone biosynthesis and metabolism');(19, 'Tyrosine metabolism');(19, 'Tryptophan metabolism')</t>
   </si>
 </sst>
 </file>
@@ -387,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -410,46 +386,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>0.03854649878506737</v>
-      </c>
-      <c r="C2">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3">
-        <v>0.04694057874972388</v>
-      </c>
-      <c r="C3">
-        <v>84</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
